--- a/experiment_results/wedos_grid/rtt_bursts_S3_atk1pct_wu300000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S3_atk1pct_wu300000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
